--- a/Backlog.xlsx
+++ b/Backlog.xlsx
@@ -1,27 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\API\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DSM\Downloads\juli\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{24707B68-AB11-43E6-9716-E08C0D640BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86DAC3C6-8C37-437E-8C87-FFAF979BEB56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{249172B4-AFE2-4710-A6D1-4965D518BEFC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{249172B4-AFE2-4710-A6D1-4965D518BEFC}"/>
   </bookViews>
   <sheets>
     <sheet name="Backlog " sheetId="1" r:id="rId1"/>
     <sheet name="Requisitos" sheetId="4" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="43">
   <si>
     <t>Prioridade</t>
   </si>
@@ -144,13 +149,19 @@
   </si>
   <si>
     <t>Qualidade na utilização do sistema</t>
+  </si>
+  <si>
+    <t>RN-01</t>
+  </si>
+  <si>
+    <t>RNF-01, RNF-02</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -281,6 +292,12 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1005,18 +1022,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B366D612-B9F7-4062-B6C5-435C569D151C}">
   <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="165.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="165.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="40.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -1036,7 +1053,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1052,14 +1069,14 @@
       <c r="E2">
         <v>1</v>
       </c>
-      <c r="F2">
-        <v>1</v>
+      <c r="F2" t="s">
+        <v>42</v>
       </c>
       <c r="G2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1075,14 +1092,14 @@
       <c r="E3">
         <v>2</v>
       </c>
-      <c r="F3">
-        <v>1</v>
+      <c r="F3" t="s">
+        <v>27</v>
       </c>
       <c r="G3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1098,14 +1115,14 @@
       <c r="E4">
         <v>2</v>
       </c>
-      <c r="F4">
-        <v>1</v>
+      <c r="F4" t="s">
+        <v>27</v>
       </c>
       <c r="G4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1121,11 +1138,14 @@
       <c r="E5">
         <v>3</v>
       </c>
+      <c r="F5" t="s">
+        <v>28</v>
+      </c>
       <c r="G5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1141,11 +1161,15 @@
       <c r="E6">
         <v>4</v>
       </c>
+      <c r="F6" t="s">
+        <v>41</v>
+      </c>
       <c r="G6" t="s">
         <v>19</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
@@ -1154,19 +1178,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39EF5926-A9AE-4F79-80DB-65207CA449F3}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="93.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="45.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="93.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="45.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>20</v>
       </c>
@@ -1189,7 +1213,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>27</v>
       </c>
@@ -1212,7 +1236,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>28</v>
       </c>
@@ -1235,7 +1259,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>26</v>
       </c>

--- a/Backlog.xlsx
+++ b/Backlog.xlsx
@@ -1,32 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DSM\Downloads\juli\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\API\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86DAC3C6-8C37-437E-8C87-FFAF979BEB56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92A74288-99B5-4111-BFFC-3ACD332FABE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{249172B4-AFE2-4710-A6D1-4965D518BEFC}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{249172B4-AFE2-4710-A6D1-4965D518BEFC}"/>
   </bookViews>
   <sheets>
     <sheet name="Backlog " sheetId="1" r:id="rId1"/>
     <sheet name="Requisitos" sheetId="4" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="49">
   <si>
     <t>Prioridade</t>
   </si>
@@ -46,24 +54,12 @@
     <t>CRITÉRIO DE ACEITAÇÃO</t>
   </si>
   <si>
-    <t>Essencial</t>
-  </si>
-  <si>
     <t>Vizualização dos dados formatados</t>
   </si>
   <si>
     <t>Alta</t>
   </si>
   <si>
-    <t>Como usuário, quero conseguir ver os dados formatados no google colab para uma análise mais detalhada.</t>
-  </si>
-  <si>
-    <t>Score mais incluisivo</t>
-  </si>
-  <si>
-    <t>Como usuário, quero ter um cálculo do score populacional mais preciso, para melhorar a inclusividade do sistema.</t>
-  </si>
-  <si>
     <t>Como usuário, quero uma melhor regionalização dos dados obtidos, para melhorar as pesquisas do score.</t>
   </si>
   <si>
@@ -118,9 +114,6 @@
     <t>Coleta dos dados</t>
   </si>
   <si>
-    <t>O sistema deve otimizar a coleta e leitura dos dados para melhorar a performance da criação do score</t>
-  </si>
-  <si>
     <t>Desempenho na leitura dos dados populacionais</t>
   </si>
   <si>
@@ -151,10 +144,43 @@
     <t>Qualidade na utilização do sistema</t>
   </si>
   <si>
-    <t>RN-01</t>
-  </si>
-  <si>
-    <t>RNF-01, RNF-02</t>
+    <t>Como usuário, quero conseguir ver os dados formatados através de gráficos no google colab para uma análise mais detalhada.</t>
+  </si>
+  <si>
+    <t>O sistema deve otimizar a coleta e leitura dos dados para melhorar a performance da plotação dos gráficos</t>
+  </si>
+  <si>
+    <t>Coleta dos dados de inadimplência a partir de 15 dias</t>
+  </si>
+  <si>
+    <t>Sistema deve diferenciar os valores de carteira ativa</t>
+  </si>
+  <si>
+    <t>RNF-03</t>
+  </si>
+  <si>
+    <t>Como usuário, quero que o sistema utilize dados de BET para implementar nos cálculos de risco de crédito.</t>
+  </si>
+  <si>
+    <t>Como usuário, quero que o sistema colete também os dados de inadimplências mais recentes para melhorar a inclusividade do score.</t>
+  </si>
+  <si>
+    <t>Como usuário, quero que o sistema utilize as diferentes modalidades de crédito, para categorizar os tipos de inadimplência.</t>
+  </si>
+  <si>
+    <t>Dados implementados nos cálculos de risco de crédito</t>
+  </si>
+  <si>
+    <t>RNF-04</t>
+  </si>
+  <si>
+    <t>RNF-10</t>
+  </si>
+  <si>
+    <t>RNF-01, RNF-05</t>
+  </si>
+  <si>
+    <t>RN-03</t>
   </si>
 </sst>
 </file>
@@ -1021,19 +1047,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B366D612-B9F7-4062-B6C5-435C569D151C}">
-  <dimension ref="A1:G6"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="165.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="40.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="165.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="49.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -1053,119 +1080,165 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="D2">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="E2">
         <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="G2" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C3" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="D3">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="G3" t="s">
-        <v>10</v>
+        <v>44</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>42</v>
       </c>
       <c r="D4">
         <v>20</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D5">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="D6">
+        <v>20</v>
+      </c>
+      <c r="E6">
         <v>2</v>
       </c>
-      <c r="E6">
+      <c r="F6" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7">
+        <v>8</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+      <c r="E8">
         <v>4</v>
       </c>
-      <c r="F6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G6" t="s">
-        <v>19</v>
+      <c r="F8" t="s">
+        <v>48</v>
+      </c>
+      <c r="G8" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -1178,108 +1251,108 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39EF5926-A9AE-4F79-80DB-65207CA449F3}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="18" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="93.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="45.5546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="98.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="45.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B1" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C1" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D1" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
       </c>
       <c r="F1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F2" t="s">
+        <v>26</v>
+      </c>
+      <c r="G2" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>24</v>
       </c>
-      <c r="G1" t="s">
-        <v>25</v>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>27</v>
-      </c>
-      <c r="B2" t="s">
-        <v>29</v>
-      </c>
-      <c r="C2" t="s">
-        <v>30</v>
-      </c>
-      <c r="D2" t="s">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" t="s">
         <v>34</v>
       </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" t="s">
         <v>31</v>
-      </c>
-      <c r="G2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E4" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G4" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
